--- a/test/fixtures/totals-row.xlsx
+++ b/test/fixtures/totals-row.xlsx
@@ -416,9 +416,11 @@
       </c>
       <c r="B2">
         <f>A2*2</f>
+        <v>0</v>
       </c>
       <c r="C2">
         <f>A2+1</f>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -427,9 +429,11 @@
       </c>
       <c r="B3">
         <f>A3*2</f>
+        <v>0</v>
       </c>
       <c r="C3">
         <f>A3+1</f>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -438,9 +442,11 @@
       </c>
       <c r="B4">
         <f>A4*2</f>
+        <v>0</v>
       </c>
       <c r="C4">
         <f>A4+1</f>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -449,9 +455,11 @@
       </c>
       <c r="B5">
         <f>A5*2</f>
+        <v>0</v>
       </c>
       <c r="C5">
         <f>A5+1</f>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -460,9 +468,11 @@
       </c>
       <c r="B6">
         <f>SUM(B2:B5)</f>
+        <v>0</v>
       </c>
       <c r="C6">
         <f>A6*3</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
